--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,143 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E8" s="3">
         <v>38400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>46900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -800,50 +803,53 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E9" s="3">
         <v>14400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,50 +862,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E10" s="3">
         <v>24000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,43 +1062,46 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1102,55 +1121,58 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E15" s="3">
         <v>6200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>5400</v>
       </c>
       <c r="I15" s="3">
         <v>5400</v>
       </c>
       <c r="J15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3200</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1158,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,50 +1202,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E17" s="3">
         <v>32300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>26200</v>
       </c>
       <c r="G17" s="3">
         <v>26200</v>
       </c>
       <c r="H17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="I17" s="3">
         <v>26700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16700</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
@@ -1230,67 +1256,73 @@
       <c r="S17" s="3">
         <v>0</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E18" s="3">
         <v>6100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,106 +1343,110 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E21" s="3">
         <v>12900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1423,55 +1459,58 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3">
         <v>5800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>2300</v>
       </c>
       <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>2300</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1479,50 +1518,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6200</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3100</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
@@ -1532,58 +1574,61 @@
       <c r="S23" s="3">
         <v>0</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1591,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,50 +1695,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4500</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2400</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
@@ -1700,53 +1751,56 @@
       <c r="S26" s="3">
         <v>0</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
@@ -1756,11 +1810,14 @@
       <c r="S27" s="3">
         <v>0</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,106 +2049,112 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
@@ -2092,11 +2164,14 @@
       <c r="S33" s="3">
         <v>0</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,50 +2226,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
@@ -2204,72 +2282,78 @@
       <c r="S35" s="3">
         <v>0</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,53 +2397,54 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E41" s="3">
         <v>20600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,44 +2513,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E43" s="3">
         <v>29300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>32000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2563,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2480,44 +2572,47 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E44" s="3">
         <v>6500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3800</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,8 +2622,8 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2536,44 +2631,47 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E45" s="3">
         <v>12900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,53 +2690,56 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E46" s="3">
         <v>69100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>66800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>64100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>65100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>59400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>49300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,13 +2749,16 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="E47" s="3">
         <v>2300</v>
@@ -2666,26 +2770,26 @@
         <v>2300</v>
       </c>
       <c r="H47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I47" s="3">
         <v>2100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3900</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4000</v>
       </c>
       <c r="L47" s="3">
         <v>4000</v>
       </c>
       <c r="M47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N47" s="3">
         <v>2100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,31 +2808,34 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -2739,8 +2846,8 @@
       <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>300</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2751,8 +2858,8 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2760,44 +2867,47 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>644500</v>
+      </c>
+      <c r="E49" s="3">
         <v>635600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>628200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>617800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>587800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>559000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>564400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>571800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>539200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>511100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>501000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2807,8 +2917,8 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2816,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,53 +3044,56 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E52" s="3">
         <v>67000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>59200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>58000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>56600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>48800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>37100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2984,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,53 +3162,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>787300</v>
+      </c>
+      <c r="E54" s="3">
         <v>781500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>767300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>754100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>720300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>686500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>683300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>684300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>633100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>601700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>581000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,44 +3269,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3326,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3225,24 +3358,24 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>81600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3252,52 +3385,55 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E59" s="3">
         <v>53700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>46700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>36600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>36800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3308,53 +3444,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E60" s="3">
         <v>60700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>41100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>116900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3364,44 +3503,47 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>342500</v>
+      </c>
+      <c r="E61" s="3">
         <v>332100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>325800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>311500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>292200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>278000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>277400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>269900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>225300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>203900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>244400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3420,8 +3562,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3429,35 +3574,35 @@
         <v>37500</v>
       </c>
       <c r="E62" s="3">
+        <v>37500</v>
+      </c>
+      <c r="F62" s="3">
         <v>38300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24900</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3476,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,53 +3798,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>437500</v>
+      </c>
+      <c r="E66" s="3">
         <v>431700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>416800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>405700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>376700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>343900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>341000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>337900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>291600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>263800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>387200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3700,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3867,11 +4034,11 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>81600</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,52 +4116,55 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E72" s="3">
         <v>15600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
@@ -4002,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,8 +4352,11 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4179,43 +4364,43 @@
         <v>349800</v>
       </c>
       <c r="E76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="F76" s="3">
         <v>350500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>348400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>343600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>342700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>342300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>346400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>341400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>337900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
@@ -4226,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,111 +4470,117 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
         <v>0</v>
       </c>
@@ -4396,11 +4590,14 @@
       <c r="S81" s="3">
         <v>0</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,50 +4618,51 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E83" s="3">
         <v>6200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>5400</v>
       </c>
       <c r="I83" s="3">
         <v>5400</v>
       </c>
       <c r="J83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3200</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -4477,8 +4675,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,50 +4970,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>19700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10500</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
@@ -4810,11 +5026,14 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,44 +5054,45 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-29500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-112200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4891,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,50 +5229,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-32000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-128100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-112700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -5059,8 +5288,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,106 +5547,112 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>44000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>20800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>131800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>113600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3900</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
@@ -5417,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,149 +656,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E8" s="3">
         <v>35500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>46900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -806,53 +810,56 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E9" s="3">
         <v>13200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -865,53 +872,56 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E10" s="3">
         <v>22300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,46 +1082,49 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>1000</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1124,58 +1144,61 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E15" s="3">
         <v>6300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>5400</v>
       </c>
       <c r="J15" s="3">
         <v>5400</v>
       </c>
       <c r="K15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L15" s="3">
         <v>5200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3200</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,53 +1229,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>29000</v>
+        <v>30400</v>
       </c>
       <c r="E17" s="3">
+        <v>29900</v>
+      </c>
+      <c r="F17" s="3">
         <v>32300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>26200</v>
       </c>
       <c r="H17" s="3">
         <v>26200</v>
       </c>
       <c r="I17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="J17" s="3">
         <v>26700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16700</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
@@ -1259,70 +1286,76 @@
       <c r="T17" s="3">
         <v>0</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6500</v>
+        <v>8700</v>
       </c>
       <c r="E18" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F18" s="3">
         <v>6100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4900</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,112 +1377,116 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5300</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E21" s="3">
         <v>7600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1462,58 +1499,61 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>2300</v>
       </c>
       <c r="P22" s="3">
         <v>2300</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>2300</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1521,53 +1561,56 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6200</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
@@ -1577,61 +1620,64 @@
       <c r="T23" s="3">
         <v>0</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1639,8 +1685,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,53 +1747,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2400</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
@@ -1754,56 +1806,59 @@
       <c r="T26" s="3">
         <v>0</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
@@ -1813,11 +1868,14 @@
       <c r="T27" s="3">
         <v>0</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,112 +2119,118 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5300</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2300</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
@@ -2167,11 +2240,14 @@
       <c r="T33" s="3">
         <v>0</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,53 +2305,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2300</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
@@ -2285,75 +2364,81 @@
       <c r="T35" s="3">
         <v>0</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,56 +2484,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E41" s="3">
         <v>19500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,8 +2544,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,47 +2606,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E43" s="3">
         <v>30600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>32000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2566,8 +2659,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2575,47 +2668,50 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E44" s="3">
         <v>6800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,8 +2721,8 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2634,47 +2730,50 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E45" s="3">
         <v>13700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,56 +2792,59 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E46" s="3">
         <v>70600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>61300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>65100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>56200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>59400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>50800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>45000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2752,16 +2854,19 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E47" s="3">
         <v>1600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2300</v>
       </c>
       <c r="F47" s="3">
         <v>2300</v>
@@ -2773,26 +2878,26 @@
         <v>2300</v>
       </c>
       <c r="I47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J47" s="3">
         <v>2100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>4000</v>
       </c>
       <c r="M47" s="3">
         <v>4000</v>
       </c>
       <c r="N47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O47" s="3">
         <v>2100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,34 +2916,37 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E48" s="3">
         <v>7800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>300</v>
@@ -2849,8 +2957,8 @@
       <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>300</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2861,8 +2969,8 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2870,47 +2978,50 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>640600</v>
+      </c>
+      <c r="E49" s="3">
         <v>644500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>635600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>628200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>617800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>587800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>559000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>564400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>571800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>539200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>511100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>501000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2920,8 +3031,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,56 +3164,59 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E52" s="3">
         <v>62800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>59200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>56600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>37100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>32500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,56 +3288,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>783500</v>
+      </c>
+      <c r="E54" s="3">
         <v>787300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>781500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>767300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>754100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>720300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>686500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>683300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>684300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>633100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>601700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>581000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3">
         <v>300</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,47 +3400,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3361,24 +3495,24 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>81600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3388,55 +3522,58 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E59" s="3">
         <v>48800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>53700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>36600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>36800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3447,56 +3584,59 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E60" s="3">
         <v>56200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>116900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,47 +3646,50 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>330800</v>
+      </c>
+      <c r="E61" s="3">
         <v>342500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>332100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>325800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>311500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>292200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>278000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>277400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>269900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>225300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>203900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>244400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3565,47 +3708,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>37500</v>
+        <v>37900</v>
       </c>
       <c r="E62" s="3">
         <v>37500</v>
       </c>
       <c r="F62" s="3">
+        <v>37500</v>
+      </c>
+      <c r="G62" s="3">
         <v>38300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>36200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24900</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,56 +3956,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>430500</v>
+      </c>
+      <c r="E66" s="3">
         <v>437500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>431700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>416800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>405700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>376700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>343900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>341000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>337900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>291600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>263800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>387200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,11 +4205,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>81600</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,55 +4290,58 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E72" s="3">
         <v>12600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-700</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,55 +4538,58 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>349800</v>
+        <v>353000</v>
       </c>
       <c r="E76" s="3">
         <v>349800</v>
       </c>
       <c r="F76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="G76" s="3">
         <v>350500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>348400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>343600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>342700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>342300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>346400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>341400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>337900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>112200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,117 +4662,123 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2300</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
@@ -4593,11 +4788,14 @@
       <c r="T81" s="3">
         <v>0</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,53 +4817,54 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E83" s="3">
         <v>6300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5400</v>
       </c>
       <c r="J83" s="3">
         <v>5400</v>
       </c>
       <c r="K83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,53 +5187,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E89" s="3">
         <v>3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10500</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
@@ -5029,11 +5246,14 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,47 +5275,48 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-112200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,53 +5459,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-32000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-128100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-112700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,112 +5793,118 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E100" s="3">
         <v>10000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>13300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>6500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>44000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>20800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>131800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>113600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3900</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,156 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E8" s="3">
         <v>39100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>31800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>25600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -813,56 +817,59 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E9" s="3">
         <v>14300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,56 +882,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E10" s="3">
         <v>24800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11900</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,8 +947,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,49 +1102,52 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1147,8 +1167,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,52 +1179,52 @@
         <v>6400</v>
       </c>
       <c r="E15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F15" s="3">
         <v>6300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5400</v>
       </c>
       <c r="K15" s="3">
         <v>5400</v>
       </c>
       <c r="L15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M15" s="3">
         <v>5200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3200</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,56 +1256,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E17" s="3">
         <v>30400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>26200</v>
       </c>
       <c r="I17" s="3">
         <v>26200</v>
       </c>
       <c r="J17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K17" s="3">
         <v>26700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16700</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
@@ -1289,73 +1316,79 @@
       <c r="U17" s="3">
         <v>0</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>8700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,118 +1411,122 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E21" s="3">
         <v>15700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1502,61 +1539,64 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
         <v>5200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>2300</v>
       </c>
       <c r="Q22" s="3">
         <v>2300</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>2300</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1564,56 +1604,59 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6200</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
@@ -1623,64 +1666,67 @@
       <c r="U23" s="3">
         <v>0</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1688,8 +1734,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,56 +1799,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>7700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2400</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
@@ -1809,59 +1861,62 @@
       <c r="U26" s="3">
         <v>0</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2300</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
@@ -1871,11 +1926,14 @@
       <c r="U27" s="3">
         <v>0</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,118 +2189,124 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2300</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
@@ -2243,11 +2316,14 @@
       <c r="U33" s="3">
         <v>0</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,56 +2384,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2300</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
@@ -2367,78 +2446,84 @@
       <c r="U35" s="3">
         <v>0</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,59 +2571,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
         <v>18100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,8 +2634,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,50 +2699,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E43" s="3">
         <v>33200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>32000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2662,8 +2755,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2671,50 +2764,53 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E44" s="3">
         <v>6300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2820,8 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2733,50 +2829,53 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E45" s="3">
         <v>13200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,59 +2894,62 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E46" s="3">
         <v>70900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>70600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>69100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>61300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>66800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>64100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>65100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>56200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>59400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>50800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>49300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,19 +2959,22 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2300</v>
       </c>
       <c r="G47" s="3">
         <v>2300</v>
@@ -2881,26 +2986,26 @@
         <v>2300</v>
       </c>
       <c r="J47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>4000</v>
       </c>
       <c r="N47" s="3">
         <v>4000</v>
       </c>
       <c r="O47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P47" s="3">
         <v>2100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2919,37 +3024,40 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E48" s="3">
         <v>7500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
@@ -2960,8 +3068,8 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>300</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2972,8 +3080,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2981,50 +3089,53 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>634700</v>
+      </c>
+      <c r="E49" s="3">
         <v>640600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>644500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>635600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>628200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>617800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>587800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>559000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>564400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>571800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>539200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>511100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>501000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3034,8 +3145,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,59 +3284,62 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E52" s="3">
         <v>63000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>67700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>59200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>58000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>56600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>37100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,59 +3414,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>768200</v>
+      </c>
+      <c r="E54" s="3">
         <v>783500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>787300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>781500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>767300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>754100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>720300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>686500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>683300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>684300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>633100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>601700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>581000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,50 +3531,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E57" s="3">
         <v>9000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3594,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3498,24 +3632,24 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>81600</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,58 +3659,61 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E59" s="3">
         <v>51400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>41200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>36600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>36800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3587,59 +3724,62 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E60" s="3">
         <v>60400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>56200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>60700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>39000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>116900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,50 +3789,53 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>324100</v>
+      </c>
+      <c r="E61" s="3">
         <v>330800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>342500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>332100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>325800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>311500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>292200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>278000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>277400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>269900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>225300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>203900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>244400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3711,50 +3854,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E62" s="3">
         <v>37900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>37500</v>
       </c>
       <c r="F62" s="3">
         <v>37500</v>
       </c>
       <c r="G62" s="3">
+        <v>37500</v>
+      </c>
+      <c r="H62" s="3">
         <v>38300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24900</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,59 +4114,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>415100</v>
+      </c>
+      <c r="E66" s="3">
         <v>430500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>437500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>431700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>416800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>405700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>376700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>343900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>341000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>337900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>291600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>263800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>387200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>81600</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,58 +4464,61 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E72" s="3">
         <v>15400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,8 +4724,11 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4550,49 +4736,49 @@
         <v>353000</v>
       </c>
       <c r="E76" s="3">
-        <v>349800</v>
+        <v>353000</v>
       </c>
       <c r="F76" s="3">
         <v>349800</v>
       </c>
       <c r="G76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="H76" s="3">
         <v>350500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>348400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>343600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>342700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>342300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>346400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>341400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>337900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>112200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,123 +4854,129 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2300</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
@@ -4791,11 +4986,14 @@
       <c r="U81" s="3">
         <v>0</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5016,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4827,47 +5026,47 @@
         <v>6400</v>
       </c>
       <c r="E83" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F83" s="3">
         <v>6300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5400</v>
       </c>
       <c r="K83" s="3">
         <v>5400</v>
       </c>
       <c r="L83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,56 +5404,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E89" s="3">
         <v>13800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10500</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
@@ -5249,11 +5466,14 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,50 +5496,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-112200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,56 +5689,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-32000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-128100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-112700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -5524,8 +5754,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,118 +6039,124 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>19200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>6500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>44000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>20800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>131800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>113600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3900</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,163 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E8" s="3">
         <v>34300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>39100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>31800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>25600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21600</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -820,59 +824,62 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E9" s="3">
         <v>13300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,59 +892,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E10" s="3">
         <v>21000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24000</v>
       </c>
-      <c r="H10" s="3">
-        <v>18300</v>
-      </c>
       <c r="I10" s="3">
+        <v>18400</v>
+      </c>
+      <c r="J10" s="3">
         <v>22500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -950,8 +960,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +988,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1054,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,52 +1122,55 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1170,8 +1190,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,52 +1205,52 @@
         <v>6400</v>
       </c>
       <c r="F15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G15" s="3">
         <v>6300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5400</v>
       </c>
       <c r="L15" s="3">
         <v>5400</v>
       </c>
       <c r="M15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N15" s="3">
         <v>5200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3200</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1235,8 +1258,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,59 +1283,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E17" s="3">
         <v>29400</v>
       </c>
-      <c r="E17" s="3">
-        <v>30400</v>
-      </c>
       <c r="F17" s="3">
-        <v>29900</v>
+        <v>29800</v>
       </c>
       <c r="G17" s="3">
-        <v>32300</v>
+        <v>29000</v>
       </c>
       <c r="H17" s="3">
+        <v>29600</v>
+      </c>
+      <c r="I17" s="3">
         <v>28700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>26200</v>
       </c>
       <c r="J17" s="3">
         <v>26200</v>
       </c>
       <c r="K17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="L17" s="3">
         <v>26700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16700</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
@@ -1319,76 +1346,82 @@
       <c r="V17" s="3">
         <v>0</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>7200</v>
+      </c>
+      <c r="O18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>200</v>
+      </c>
+      <c r="R18" s="3">
+        <v>8200</v>
+      </c>
+      <c r="S18" s="3">
         <v>4900</v>
       </c>
-      <c r="E18" s="3">
-        <v>8700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>6100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>6600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>7200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>2700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>8000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>8200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>4900</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,124 +1445,128 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>5800</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>10700</v>
+        <v>16500</v>
       </c>
       <c r="E21" s="3">
-        <v>15700</v>
+        <v>11200</v>
       </c>
       <c r="F21" s="3">
-        <v>7600</v>
+        <v>15600</v>
       </c>
       <c r="G21" s="3">
         <v>12900</v>
       </c>
       <c r="H21" s="3">
-        <v>11000</v>
+        <v>15000</v>
       </c>
       <c r="I21" s="3">
-        <v>12700</v>
+        <v>9200</v>
       </c>
       <c r="J21" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K21" s="3">
         <v>9100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1542,64 +1579,67 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>9600</v>
+      </c>
+      <c r="H22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>4700</v>
-      </c>
       <c r="I22" s="3">
-        <v>4200</v>
+        <v>2900</v>
       </c>
       <c r="J22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K22" s="3">
         <v>4100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2800</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>2300</v>
       </c>
       <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>2300</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1607,59 +1647,62 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6200</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
@@ -1669,67 +1712,70 @@
       <c r="V23" s="3">
         <v>0</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1737,8 +1783,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,59 +1851,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>7700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2400</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
@@ -1864,62 +1916,65 @@
       <c r="V26" s="3">
         <v>0</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
@@ -1929,11 +1984,14 @@
       <c r="V27" s="3">
         <v>0</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2055,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2123,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,124 +2259,130 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2300</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
@@ -2319,11 +2392,14 @@
       <c r="V33" s="3">
         <v>0</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,59 +2463,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2300</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
@@ -2449,81 +2528,87 @@
       <c r="V35" s="3">
         <v>0</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,62 +2658,63 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,8 +2724,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,53 +2792,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E43" s="3">
         <v>32100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>32000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,8 +2851,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2767,53 +2860,56 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E44" s="3">
         <v>6200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2823,8 +2919,8 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2832,53 +2928,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2897,62 +2996,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E46" s="3">
         <v>67500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>70900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>69100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>66800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>64100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>65100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>56200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>59400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>50800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>49300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>45000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,53 +3064,56 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="E47" s="3">
-        <v>1500</v>
+        <v>6500</v>
       </c>
       <c r="F47" s="3">
-        <v>1600</v>
+        <v>7200</v>
       </c>
       <c r="G47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K47" s="3">
         <v>2300</v>
       </c>
-      <c r="H47" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>4000</v>
       </c>
       <c r="O47" s="3">
         <v>4000</v>
       </c>
       <c r="P47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,40 +3132,43 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
@@ -3071,8 +3179,8 @@
       <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>300</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -3083,8 +3191,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3092,53 +3200,56 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>637400</v>
+      </c>
+      <c r="E49" s="3">
         <v>634700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>640600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>644500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>635600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>628200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>617800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>587800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>559000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>564400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>571800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>539200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>511100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>501000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3259,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3157,8 +3268,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,62 +3404,65 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F52" s="3">
         <v>57300</v>
       </c>
-      <c r="E52" s="3">
-        <v>63000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>62800</v>
-      </c>
       <c r="G52" s="3">
-        <v>67000</v>
+        <v>57800</v>
       </c>
       <c r="H52" s="3">
-        <v>67700</v>
+        <v>57800</v>
       </c>
       <c r="I52" s="3">
-        <v>59200</v>
+        <v>59100</v>
       </c>
       <c r="J52" s="3">
+        <v>52500</v>
+      </c>
+      <c r="K52" s="3">
         <v>58000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>56600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>48800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>37100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3472,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,62 +3540,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>778200</v>
+      </c>
+      <c r="E54" s="3">
         <v>768200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>783500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>787300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>781500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>767300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>754100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>720300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>686500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>683300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>684300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>633100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>601700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>581000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3608,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,53 +3662,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>5100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3728,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3609,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -3621,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3635,24 +3769,24 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>81600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3662,61 +3796,64 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>47600</v>
+        <v>5800</v>
       </c>
       <c r="E59" s="3">
-        <v>51400</v>
+        <v>8000</v>
       </c>
       <c r="F59" s="3">
-        <v>48800</v>
+        <v>7900</v>
       </c>
       <c r="G59" s="3">
-        <v>53700</v>
+        <v>10000</v>
       </c>
       <c r="H59" s="3">
-        <v>46700</v>
+        <v>12800</v>
       </c>
       <c r="I59" s="3">
-        <v>47900</v>
+        <v>13000</v>
       </c>
       <c r="J59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K59" s="3">
         <v>41200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>30900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>36600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>36800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>31000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
@@ -3727,62 +3864,65 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E60" s="3">
         <v>52700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>60700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>51500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>116900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3792,53 +3932,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>324100</v>
+        <v>331600</v>
       </c>
       <c r="E61" s="3">
-        <v>330800</v>
+        <v>330600</v>
       </c>
       <c r="F61" s="3">
-        <v>342500</v>
+        <v>337600</v>
       </c>
       <c r="G61" s="3">
-        <v>332100</v>
+        <v>349400</v>
       </c>
       <c r="H61" s="3">
-        <v>325800</v>
+        <v>338700</v>
       </c>
       <c r="I61" s="3">
-        <v>311500</v>
+        <v>332700</v>
       </c>
       <c r="J61" s="3">
+        <v>318600</v>
+      </c>
+      <c r="K61" s="3">
         <v>292200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>278000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>277400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>269900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>225300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>203900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>244400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3857,53 +4000,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>36900</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
-        <v>37900</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>37500</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>37500</v>
+        <v>600</v>
       </c>
       <c r="H62" s="3">
-        <v>38300</v>
+        <v>600</v>
       </c>
       <c r="I62" s="3">
-        <v>38400</v>
+        <v>700</v>
       </c>
       <c r="J62" s="3">
+        <v>800</v>
+      </c>
+      <c r="K62" s="3">
         <v>36200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24900</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3922,8 +4068,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,62 +4272,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>415100</v>
+        <v>419000</v>
       </c>
       <c r="E66" s="3">
-        <v>430500</v>
+        <v>413700</v>
       </c>
       <c r="F66" s="3">
-        <v>437500</v>
+        <v>429000</v>
       </c>
       <c r="G66" s="3">
-        <v>431700</v>
+        <v>436100</v>
       </c>
       <c r="H66" s="3">
-        <v>416800</v>
+        <v>430300</v>
       </c>
       <c r="I66" s="3">
-        <v>405700</v>
+        <v>415600</v>
       </c>
       <c r="J66" s="3">
+        <v>404400</v>
+      </c>
+      <c r="K66" s="3">
         <v>376700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>343900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>341000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>337900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>291600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>263800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>387200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,8 +4340,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4379,11 +4547,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>81600</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,61 +4638,64 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E72" s="3">
         <v>15100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4532,8 +4706,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,61 +4910,64 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>353000</v>
+        <v>357900</v>
       </c>
       <c r="E76" s="3">
         <v>353000</v>
       </c>
       <c r="F76" s="3">
-        <v>349800</v>
+        <v>353000</v>
       </c>
       <c r="G76" s="3">
         <v>349800</v>
       </c>
       <c r="H76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="I76" s="3">
         <v>350500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>348400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>343600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>342700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>342300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>346400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>341400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>337900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>112200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4978,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,129 +5046,135 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2300</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
@@ -4989,11 +5184,14 @@
       <c r="V81" s="3">
         <v>0</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,59 +5215,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6400</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>6400</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>6200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>5500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5400</v>
       </c>
       <c r="L83" s="3">
         <v>5400</v>
       </c>
       <c r="M83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N83" s="3">
         <v>5200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3200</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -5082,8 +5281,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,59 +5621,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E89" s="3">
         <v>8600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>19700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10500</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -5469,11 +5686,14 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,53 +5717,54 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-14500</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-17300</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-15200</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-26800</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-29500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-112200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5562,8 +5783,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,59 +5919,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-128100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-112700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -5757,8 +5987,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,31 +6015,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5847,8 +6081,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,124 +6285,130 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>19200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>6500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>44000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>20800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>131800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>113600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>9000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K101" s="3">
+        <v>400</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O101" s="3">
+        <v>100</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
-        <v>100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="P101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3900</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
@@ -6172,69 +6421,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,170 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E8" s="3">
         <v>40700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>39100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>31800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21600</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -827,62 +830,65 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E9" s="3">
         <v>14800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9700</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -895,62 +901,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E10" s="3">
         <v>25800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11900</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -963,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,55 +1141,58 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1193,13 +1212,16 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="E15" s="3">
         <v>6400</v>
@@ -1208,52 +1230,52 @@
         <v>6400</v>
       </c>
       <c r="G15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="H15" s="3">
         <v>6300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>5400</v>
       </c>
       <c r="M15" s="3">
         <v>5400</v>
       </c>
       <c r="N15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O15" s="3">
         <v>5200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3200</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1261,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,62 +1309,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E17" s="3">
         <v>30500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>26200</v>
       </c>
       <c r="K17" s="3">
         <v>26200</v>
       </c>
       <c r="L17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="M17" s="3">
         <v>26700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16700</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
@@ -1349,79 +1375,85 @@
       <c r="W17" s="3">
         <v>0</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E18" s="3">
         <v>10100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,23 +1478,24 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1470,106 +1503,109 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E21" s="3">
         <v>16500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,67 +1618,70 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>10100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>2300</v>
       </c>
       <c r="S22" s="3">
         <v>2300</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>2300</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1650,62 +1689,65 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6200</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
@@ -1715,70 +1757,73 @@
       <c r="W23" s="3">
         <v>0</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1786,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,62 +1902,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4500</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>7700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2400</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
@@ -1919,65 +1970,68 @@
       <c r="W26" s="3">
         <v>0</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
@@ -1987,11 +2041,14 @@
       <c r="W27" s="3">
         <v>0</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,23 +2328,26 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2286,106 +2355,109 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2300</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
@@ -2395,11 +2467,14 @@
       <c r="W33" s="3">
         <v>0</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,62 +2541,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2300</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
@@ -2531,84 +2609,90 @@
       <c r="W35" s="3">
         <v>0</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,65 +2744,66 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E41" s="3">
         <v>21100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2727,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,56 +2884,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E43" s="3">
         <v>36200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>32100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>33200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>30600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>32000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>31300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2854,8 +2946,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2863,56 +2955,59 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>6700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3800</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2922,8 +3017,8 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -2931,56 +3026,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E45" s="3">
         <v>13000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2999,65 +3097,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E46" s="3">
         <v>77000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>67500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>70600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>69100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>61300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>64100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>65100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>56200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>59400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>50800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>45000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3067,56 +3168,59 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3900</v>
-      </c>
-      <c r="O47" s="3">
-        <v>4000</v>
       </c>
       <c r="P47" s="3">
         <v>4000</v>
       </c>
       <c r="Q47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R47" s="3">
         <v>2100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3135,43 +3239,46 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E48" s="3">
         <v>7000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -3182,8 +3289,8 @@
       <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>300</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3194,8 +3301,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3203,56 +3310,59 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>693400</v>
+      </c>
+      <c r="E49" s="3">
         <v>637400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>634700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>640600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>644500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>635600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>628200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>617800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>587800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>559000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>564400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>571800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>539200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>511100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>501000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3262,8 +3372,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3271,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,65 +3523,68 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E52" s="3">
         <v>54200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>52200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>57300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>57800</v>
       </c>
       <c r="H52" s="3">
         <v>57800</v>
       </c>
       <c r="I52" s="3">
+        <v>57800</v>
+      </c>
+      <c r="J52" s="3">
         <v>59100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>52500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>56600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>48800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>37100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,65 +3665,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>832400</v>
+      </c>
+      <c r="E54" s="3">
         <v>778200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>768200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>783500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>787300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>781500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>767300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>754100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>720300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>686500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>683300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>684300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>633100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>601700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>581000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3">
         <v>300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3611,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,56 +3792,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3731,8 +3861,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3743,11 +3876,11 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -3755,11 +3888,11 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3772,24 +3905,24 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>81600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,64 +3932,67 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E59" s="3">
         <v>5800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>30900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>36600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>36800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>28600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>31000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -3867,65 +4003,68 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E60" s="3">
         <v>56000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>52700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>60400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>56200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>54500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>116900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3">
         <v>200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3935,56 +4074,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>377700</v>
+      </c>
+      <c r="E61" s="3">
         <v>331600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>330600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>337600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>349400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>338700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>332700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>318600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>292200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>278000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>277400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>269900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>225300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>203900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>244400</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4003,19 +4145,22 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>600</v>
       </c>
       <c r="G62" s="3">
         <v>600</v>
@@ -4024,35 +4169,35 @@
         <v>600</v>
       </c>
       <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>36200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,65 +4429,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>471600</v>
+      </c>
+      <c r="E66" s="3">
         <v>419000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>413700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>429000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>436100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>430300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>415600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>404400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>376700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>343900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>341000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>337900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>291600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>263800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>387200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3">
         <v>200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4550,11 +4717,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>81600</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4573,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,64 +4811,67 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E72" s="3">
         <v>15200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-700</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4709,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,64 +5095,67 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>359500</v>
+      </c>
+      <c r="E76" s="3">
         <v>357900</v>
-      </c>
-      <c r="E76" s="3">
-        <v>353000</v>
       </c>
       <c r="F76" s="3">
         <v>353000</v>
       </c>
       <c r="G76" s="3">
-        <v>349800</v>
+        <v>353000</v>
       </c>
       <c r="H76" s="3">
         <v>349800</v>
       </c>
       <c r="I76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="J76" s="3">
         <v>350500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>348400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>343600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>342700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>342300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>346400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>341400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>337900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>112200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4981,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,135 +5237,141 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2300</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
@@ -5187,11 +5381,14 @@
       <c r="W81" s="3">
         <v>0</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5228,50 +5426,50 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>5400</v>
       </c>
       <c r="M83" s="3">
         <v>5400</v>
       </c>
       <c r="N83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O83" s="3">
         <v>5200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3200</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -5284,8 +5482,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,62 +5837,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E89" s="3">
         <v>13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>10500</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
@@ -5689,11 +5905,14 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5733,41 +5953,41 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-29500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-112200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5786,8 +6006,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,62 +6148,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-128100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-112700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21400</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -5990,8 +6219,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6042,8 +6275,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6084,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,130 +6530,136 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>19200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>6500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>44000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>20800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>131800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>113600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3900</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -6424,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
-      <c r="X102" s="3" t="s">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,245 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F8" s="3">
         <v>42300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>40700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>34300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>39100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>35500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>38400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>31800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>34800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>29900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>33300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>24300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>33600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>25800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>46900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>25600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>21600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F9" s="3">
         <v>15100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>14800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>13300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>14300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>13200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>14400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>13500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>12300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>11800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>13900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>10000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>13000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>11400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>19800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>7700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>9700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,68 +918,74 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E10" s="3">
         <v>27200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
+        <v>27200</v>
+      </c>
+      <c r="G10" s="3">
         <v>25800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>21000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>24800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>22300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>24000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>18400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>22500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>18100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>19400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>14300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>20600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>14400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>27100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>8900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>16400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>11900</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -975,8 +995,14 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1028,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1101,14 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,61 +1178,67 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>500</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>600</v>
+      </c>
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1215,79 +1255,91 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F15" s="3">
         <v>6700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>6400</v>
       </c>
       <c r="G15" s="3">
         <v>6400</v>
       </c>
       <c r="H15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J15" s="3">
         <v>6300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>6200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>6100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>5800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>5500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>5400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>5400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>5200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>5000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>8800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>4100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>3700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>3200</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1362,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F17" s="3">
         <v>32700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>30500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>29400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>29800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>29000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>29600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>28700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>26200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>26200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>26700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>26400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>38900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>17400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>16700</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
       <c r="X17" s="3">
         <v>0</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F18" s="3">
         <v>9600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>10100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>9400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>6500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>8800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>7200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>8000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>8200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>4900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,139 +1545,147 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>600</v>
       </c>
       <c r="S20" s="3">
         <v>1400</v>
       </c>
       <c r="T20" s="3">
+        <v>600</v>
+      </c>
+      <c r="U20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F21" s="3">
         <v>16600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>16500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>15600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>12900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>15000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>9200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>14300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>9100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>15100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>8400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>18200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>9300</v>
       </c>
       <c r="Q21" s="3">
         <v>18200</v>
       </c>
       <c r="R21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S21" s="3">
+        <v>18200</v>
+      </c>
+      <c r="T21" s="3">
         <v>4800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>13200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>8600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,221 +1695,245 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F22" s="3">
         <v>2700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>5500</v>
       </c>
-      <c r="G22" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J22" s="3">
         <v>9600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>4100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>3500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>3000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>2900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>5500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>2300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>2300</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F23" s="3">
         <v>7300</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>6200</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>7200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>3100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
       <c r="X23" s="3">
         <v>0</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>600</v>
+      </c>
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +2003,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F26" s="3">
         <v>5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4500</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>7700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2400</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>7800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2234,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2311,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2388,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2465,168 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-600</v>
       </c>
       <c r="S32" s="3">
         <v>-1400</v>
       </c>
       <c r="T32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>7800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>6100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2300</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
       <c r="X33" s="3">
         <v>0</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2696,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>7800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>6100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2300</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2888,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2917,87 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F41" s="3">
         <v>17800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>21100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>19500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>20600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>14900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>18800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>17800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>14600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>12800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>14000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,8 +3067,14 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2896,195 +3082,207 @@
         <v>34700</v>
       </c>
       <c r="E43" s="3">
+        <v>37800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>34700</v>
+      </c>
+      <c r="G43" s="3">
         <v>36200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>32100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>33200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>30600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>29300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>32000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>31300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>26800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>26400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>25600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>25200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>18500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>19300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>14000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>6700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6200</v>
       </c>
-      <c r="G44" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>6800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>4500</v>
-      </c>
-      <c r="O44" s="3">
-        <v>4000</v>
       </c>
       <c r="P44" s="3">
         <v>4500</v>
       </c>
       <c r="Q44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R44" s="3">
+        <v>4500</v>
+      </c>
+      <c r="S44" s="3">
         <v>4400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3800</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F45" s="3">
         <v>21600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>13000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>12900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="K45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="L45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>15200</v>
+      </c>
+      <c r="N45" s="3">
+        <v>14400</v>
+      </c>
+      <c r="O45" s="3">
+        <v>13900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>12400</v>
+      </c>
+      <c r="R45" s="3">
+        <v>13100</v>
+      </c>
+      <c r="S45" s="3">
+        <v>12800</v>
+      </c>
+      <c r="T45" s="3">
         <v>13200</v>
       </c>
-      <c r="H45" s="3">
-        <v>13700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>12900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>11900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>15200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>14400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>13900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>13500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>12400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>13100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>12800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>13200</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,79 +3298,91 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>79300</v>
+      </c>
+      <c r="F46" s="3">
         <v>74000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>77000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>67500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>70900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>70600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>69100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>61300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>66800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>64100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>65100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>56200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>59400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>50800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>49300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>45000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3180,53 +3390,53 @@
         <v>3700</v>
       </c>
       <c r="E47" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G47" s="3">
         <v>2600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>6500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>7200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>6600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>11500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>9100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>4000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3242,49 +3452,55 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F48" s="3">
         <v>6600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>7500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7800</v>
       </c>
       <c r="I48" s="3">
         <v>7500</v>
       </c>
       <c r="J48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L48" s="3">
         <v>7700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>300</v>
-      </c>
-      <c r="P48" s="3">
-        <v>300</v>
       </c>
       <c r="Q48" s="3">
         <v>300</v>
@@ -3292,11 +3508,11 @@
       <c r="R48" s="3">
         <v>300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>300</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3304,88 +3520,100 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>721800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>720100</v>
+      </c>
+      <c r="F49" s="3">
         <v>693400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>637400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>634700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>640600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>644500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>635600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>628200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>617800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>587800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>559000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>564400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>571800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>539200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>511100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>501000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3683,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3760,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>56500</v>
+      </c>
+      <c r="F52" s="3">
         <v>54600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>54200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>52200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>57300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>57800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>57800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>59100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>52500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>58000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>57900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>56600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>48800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>38700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>37100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>32500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3914,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>857000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>865100</v>
+      </c>
+      <c r="F54" s="3">
         <v>832400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>778200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>768200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>783500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>787300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>781500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>767300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>754100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>720300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>686500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>683300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>684300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>633100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>601700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>581000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3">
         <v>300</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4024,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +4053,64 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +4126,14 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3873,32 +4141,32 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3908,97 +4176,103 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>81600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F59" s="3">
         <v>12800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>8000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>7900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>10000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>41200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>34900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>30900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>36600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>36800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>28600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>31000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
@@ -4006,133 +4280,145 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>65800</v>
+      </c>
+      <c r="F60" s="3">
         <v>61700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>56000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>52700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>60400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>56200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>60700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>51500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>54500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>47100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>39000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>36200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>41100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>41900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>33900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>116900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>393500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>394300</v>
+      </c>
+      <c r="F61" s="3">
         <v>377700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>331600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>330600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>337600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>349400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>338700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>332700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>318600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>292200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>278000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>277400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>269900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>225300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>203900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>244400</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,62 +4434,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>600</v>
+      </c>
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>600</v>
       </c>
       <c r="I62" s="3">
         <v>600</v>
       </c>
       <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
+        <v>600</v>
+      </c>
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>36200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>26000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>26400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>25900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>23300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>25000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>24900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4511,14 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4588,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4665,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4742,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>486900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>498900</v>
+      </c>
+      <c r="F66" s="3">
         <v>471600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>419000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>413700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>429000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>436100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>430300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>415600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>404400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>376700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>343900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>341000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>337900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>291600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>263800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>387200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4852,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4925,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5002,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4720,14 +5056,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>81600</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +5079,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,70 +5156,76 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>23100</v>
+      </c>
+      <c r="F72" s="3">
         <v>20500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>15200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>15100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>15400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>12600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>15600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>15000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>14800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>12400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>16800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>12300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>12200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -4885,8 +5233,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5310,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5387,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,70 +5464,76 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>368900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>364900</v>
+      </c>
+      <c r="F76" s="3">
         <v>359500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>357900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>353000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>353000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>349800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>349800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>350500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>348400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>343600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>342700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>342300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>346400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>341400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>337900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>112200</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3">
-        <v>0</v>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5169,8 +5541,14 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5618,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>7800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>6100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2300</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
       <c r="X81" s="3">
         <v>0</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5810,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5429,7 +5827,7 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5438,44 +5836,44 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>5500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>5400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>5400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>5000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>8900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>4100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>3700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>3200</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
@@ -5485,8 +5883,14 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5960,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6037,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6114,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6191,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6268,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F89" s="3">
         <v>11200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>8600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>13800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>19700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>14600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>9800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>12700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>10500</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6378,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5956,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -5965,35 +6407,35 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-29500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-36700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-13500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-112200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -6009,8 +6451,14 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6528,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,68 +6605,74 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-61200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-8800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-14700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-17300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-15200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-26800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-29500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-36700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-128100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-112700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-12800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-21400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -6222,8 +6682,14 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6715,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6278,11 +6746,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6320,8 +6788,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6865,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6942,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,139 +7019,151 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F100" s="3">
         <v>46900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-8400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-12000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>10000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>6300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>13300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>19200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>12700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>6500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>44000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>20800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>131800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>113600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>9000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>10000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>-400</v>
+        <v>200</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>3900</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
@@ -6675,75 +7173,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>3200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>3100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,197 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E8" s="3">
         <v>45400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>25800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21600</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -854,74 +857,77 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E9" s="3">
         <v>16500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9700</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -934,74 +940,77 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E10" s="3">
         <v>28900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>27200</v>
       </c>
       <c r="G10" s="3">
         <v>27200</v>
       </c>
       <c r="H10" s="3">
+        <v>27200</v>
+      </c>
+      <c r="I10" s="3">
         <v>25800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>27100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11900</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1014,8 +1023,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,56 +1234,56 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1284,25 +1303,28 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E15" s="3">
         <v>7600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>6400</v>
       </c>
       <c r="I15" s="3">
         <v>6400</v>
@@ -1311,52 +1333,52 @@
         <v>6400</v>
       </c>
       <c r="K15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L15" s="3">
         <v>6300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5500</v>
-      </c>
-      <c r="P15" s="3">
-        <v>5400</v>
       </c>
       <c r="Q15" s="3">
         <v>5400</v>
       </c>
       <c r="R15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="S15" s="3">
         <v>5200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3200</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1364,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,74 +1416,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E17" s="3">
         <v>34700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>26200</v>
       </c>
       <c r="O17" s="3">
         <v>26200</v>
       </c>
       <c r="P17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="Q17" s="3">
         <v>26700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>38900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16700</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
@@ -1468,91 +1494,97 @@
       <c r="AA17" s="3">
         <v>0</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4900</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA18" s="3">
         <v>0</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,35 +1613,36 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1617,118 +1650,121 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E21" s="3">
         <v>17800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>18200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1741,79 +1777,82 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E22" s="3">
         <v>7100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2800</v>
-      </c>
-      <c r="V22" s="3">
-        <v>2300</v>
       </c>
       <c r="W22" s="3">
         <v>2300</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>2300</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1821,74 +1860,77 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7300</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>10200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3100</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
         <v>0</v>
       </c>
@@ -1898,82 +1940,85 @@
       <c r="AA23" s="3">
         <v>0</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -1981,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,8 +2109,11 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2070,65 +2121,65 @@
         <v>2200</v>
       </c>
       <c r="E26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4500</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>7700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2400</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
         <v>0</v>
       </c>
@@ -2138,77 +2189,80 @@
       <c r="AA26" s="3">
         <v>0</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2300</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
         <v>0</v>
       </c>
@@ -2218,11 +2272,14 @@
       <c r="AA27" s="3">
         <v>0</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2381,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,35 +2607,38 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2577,118 +2646,121 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2300</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
         <v>0</v>
       </c>
@@ -2698,11 +2770,14 @@
       <c r="AA33" s="3">
         <v>0</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,74 +2856,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2300</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
         <v>0</v>
       </c>
@@ -2858,96 +2936,102 @@
       <c r="AA35" s="3">
         <v>0</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,77 +3091,78 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E41" s="3">
         <v>27900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>18800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3086,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3166,68 +3255,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E43" s="3">
         <v>35900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>34700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>37800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>32100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>33200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>32000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>31300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>26800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>26400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>25200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3237,8 +3329,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3246,8 +3338,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3263,51 +3358,51 @@
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>6700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6200</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>6800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3800</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3317,8 +3412,8 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
@@ -3326,68 +3421,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E45" s="3">
         <v>20000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,77 +3504,80 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E46" s="3">
         <v>83800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>79300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>74000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>77000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>69100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>61300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>66800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>64100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>56200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>59400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>50800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>49300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3486,68 +3587,71 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E47" s="3">
         <v>3400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3900</v>
-      </c>
-      <c r="S47" s="3">
-        <v>4000</v>
       </c>
       <c r="T47" s="3">
         <v>4000</v>
       </c>
       <c r="U47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V47" s="3">
         <v>2100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3566,55 +3670,58 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
@@ -3625,8 +3732,8 @@
       <c r="U48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>300</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3637,8 +3744,8 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3646,68 +3753,71 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>797200</v>
+      </c>
+      <c r="E49" s="3">
         <v>752500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>721800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>720100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>693400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>637400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>634700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>640600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>644500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>635600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>628200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>617800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>587800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>559000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>564400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>571800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>539200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>511100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>501000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3827,8 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3726,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,77 +4002,80 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E52" s="3">
         <v>56700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>56500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>54600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>52200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>57800</v>
       </c>
       <c r="L52" s="3">
         <v>57800</v>
       </c>
       <c r="M52" s="3">
+        <v>57800</v>
+      </c>
+      <c r="N52" s="3">
         <v>59100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>52500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>57900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>56600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>48800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>38700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>37100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>32500</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3966,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,77 +4168,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>941900</v>
+      </c>
+      <c r="E54" s="3">
         <v>903500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>857000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>865100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>832400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>778200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>768200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>783500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>787300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>781500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>767300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>754100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>720300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>686500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>683300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>684300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>633100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>601700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>581000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4126,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,68 +4315,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>5400</v>
       </c>
       <c r="G57" s="3">
         <v>5400</v>
       </c>
       <c r="H57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4266,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4278,11 +4411,11 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -4290,11 +4423,11 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4302,11 +4435,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4319,24 +4452,24 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
         <v>81600</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4346,76 +4479,79 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E59" s="3">
         <v>8300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>30900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>36600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>36800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>28600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>31000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
@@ -4426,77 +4562,80 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E60" s="3">
         <v>61900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>65800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>60400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>60700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>54500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>41900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>33900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>116900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3">
         <v>200</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4506,68 +4645,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>460300</v>
+      </c>
+      <c r="E61" s="3">
         <v>429200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>393500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>394300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>377700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>331600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>330600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>337600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>349400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>338700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>332700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>318600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>292200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>278000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>277400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>269900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>225300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>203900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>244400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4586,31 +4728,34 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
         <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G62" s="3">
         <v>600</v>
       </c>
       <c r="H62" s="3">
+        <v>600</v>
+      </c>
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>600</v>
       </c>
       <c r="K62" s="3">
         <v>600</v>
@@ -4619,35 +4764,35 @@
         <v>600</v>
       </c>
       <c r="M62" s="3">
+        <v>600</v>
+      </c>
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>36200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,77 +5060,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>567100</v>
+      </c>
+      <c r="E66" s="3">
         <v>531400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>486900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>498900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>471600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>419000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>413700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>429000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>436100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>430300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>415600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>404400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>376700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>343900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>341000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>337900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>291600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>263800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>387200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3">
         <v>200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4986,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5233,11 +5400,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>81600</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5256,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,76 +5506,79 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3">
+        <v>0</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
@@ -5416,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,76 +5838,79 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>373600</v>
+      </c>
+      <c r="E76" s="3">
         <v>370900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>368900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>364900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>359500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>357900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>353000</v>
       </c>
       <c r="J76" s="3">
         <v>353000</v>
       </c>
       <c r="K76" s="3">
-        <v>349800</v>
+        <v>353000</v>
       </c>
       <c r="L76" s="3">
         <v>349800</v>
       </c>
       <c r="M76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="N76" s="3">
         <v>350500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>348400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>343600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>342700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>342300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>346400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>341400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>337900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>112200</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3">
+        <v>0</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
@@ -5736,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,159 +6004,165 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2300</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
         <v>0</v>
       </c>
@@ -5978,11 +6172,14 @@
       <c r="AA81" s="3">
         <v>0</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6035,50 +6233,50 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>5400</v>
       </c>
       <c r="Q83" s="3">
         <v>5400</v>
       </c>
       <c r="R83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="S83" s="3">
         <v>5200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3200</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
@@ -6091,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,74 +6704,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E89" s="3">
         <v>19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10500</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
@@ -6568,11 +6784,14 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,8 +6820,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6610,7 +6830,7 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -6628,41 +6848,41 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-29500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-36700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-112200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -6681,8 +6901,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,74 +7067,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-40400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-36700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-32000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-128100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-112700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21400</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -6921,8 +7150,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6989,8 +7222,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7031,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,154 +7513,160 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E100" s="3">
         <v>34000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>46900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>19200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>6500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>44000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>20800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>131800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>113600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>10000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3900</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -7431,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E102" s="3">
         <v>13100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>RSVR</t>
   </si>
@@ -656,203 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E8" s="3">
         <v>45600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>46900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>25600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
@@ -860,77 +864,80 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E9" s="3">
         <v>16200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9700</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -943,77 +950,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E10" s="3">
         <v>29400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>27200</v>
       </c>
       <c r="H10" s="3">
         <v>27200</v>
       </c>
       <c r="I10" s="3">
+        <v>27200</v>
+      </c>
+      <c r="J10" s="3">
         <v>25800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>27100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11900</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,56 +1257,56 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1306,28 +1326,31 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E15" s="3">
         <v>7800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>6400</v>
       </c>
       <c r="J15" s="3">
         <v>6400</v>
@@ -1336,52 +1359,52 @@
         <v>6400</v>
       </c>
       <c r="L15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M15" s="3">
         <v>6300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>5400</v>
       </c>
       <c r="R15" s="3">
         <v>5400</v>
       </c>
       <c r="S15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="T15" s="3">
         <v>5200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3200</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,77 +1443,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E17" s="3">
         <v>35200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>26200</v>
       </c>
       <c r="P17" s="3">
         <v>26200</v>
       </c>
       <c r="Q17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="R17" s="3">
         <v>26700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>17400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16700</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
       <c r="Z17" s="3">
         <v>0</v>
       </c>
@@ -1497,94 +1524,100 @@
       <c r="AB17" s="3">
         <v>0</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E18" s="3">
         <v>10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB18" s="3">
         <v>0</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,38 +1647,39 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1653,121 +1687,124 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E21" s="3">
         <v>17900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>18200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,82 +1817,85 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2800</v>
-      </c>
-      <c r="W22" s="3">
-        <v>2300</v>
       </c>
       <c r="X22" s="3">
         <v>2300</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>2300</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1863,77 +1903,80 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7300</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6200</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>10200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
         <v>0</v>
       </c>
@@ -1943,85 +1986,88 @@
       <c r="AB23" s="3">
         <v>0</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,77 +2161,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2200</v>
+        <v>4100</v>
       </c>
       <c r="E26" s="3">
         <v>2200</v>
       </c>
       <c r="F26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>7700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2400</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
         <v>0</v>
       </c>
@@ -2192,80 +2244,83 @@
       <c r="AB26" s="3">
         <v>0</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E27" s="3">
         <v>2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2300</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
         <v>0</v>
       </c>
@@ -2275,11 +2330,14 @@
       <c r="AB27" s="3">
         <v>0</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,38 +2677,41 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2649,121 +2719,124 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E33" s="3">
         <v>2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2300</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
         <v>0</v>
       </c>
@@ -2773,11 +2846,14 @@
       <c r="AB33" s="3">
         <v>0</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,77 +2935,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E35" s="3">
         <v>2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2300</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
         <v>0</v>
       </c>
@@ -2939,99 +3018,105 @@
       <c r="AB35" s="3">
         <v>0</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,80 +3178,81 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E41" s="3">
         <v>20600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>27900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,71 +3348,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E43" s="3">
         <v>37100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>35900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>37800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>32100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>33200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>31300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>26800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>26400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>25600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>25200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3332,8 +3425,8 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3361,51 +3457,51 @@
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>6700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6200</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
         <v>6800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3415,8 +3511,8 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
@@ -3424,71 +3520,74 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E45" s="3">
         <v>20200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,80 +3606,83 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E46" s="3">
         <v>77800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>83800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>69500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>79300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>74000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>77000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>70600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>69100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>61300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>66800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>64100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>65100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>56200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>59400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>50800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>49300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,71 +3692,74 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E47" s="3">
         <v>3200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3900</v>
-      </c>
-      <c r="T47" s="3">
-        <v>4000</v>
       </c>
       <c r="U47" s="3">
         <v>4000</v>
       </c>
       <c r="V47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W47" s="3">
         <v>2100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3673,58 +3778,61 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E48" s="3">
         <v>7800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>300</v>
       </c>
       <c r="T48" s="3">
         <v>300</v>
@@ -3735,8 +3843,8 @@
       <c r="V48" s="3">
         <v>300</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>300</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3747,8 +3855,8 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3756,71 +3864,74 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>789100</v>
+      </c>
+      <c r="E49" s="3">
         <v>797200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>752500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>721800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>720100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>693400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>637400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>634700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>640600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>644500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>635600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>628200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>617800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>587800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>559000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>564400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>571800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>539200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>511100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>501000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3830,8 +3941,8 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,80 +4122,83 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E52" s="3">
         <v>55900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>56500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>52200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>57800</v>
       </c>
       <c r="M52" s="3">
         <v>57800</v>
       </c>
       <c r="N52" s="3">
+        <v>57800</v>
+      </c>
+      <c r="O52" s="3">
         <v>59100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>52500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>58000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>57900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>56600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>48800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>38700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>37100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>32500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,80 +4294,83 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>949700</v>
+      </c>
+      <c r="E54" s="3">
         <v>941900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>903500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>857000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>865100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>832400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>778200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>768200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>783500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>787300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>781500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>767300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>754100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>720300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>686500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>683300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>684300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>633100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>601700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>581000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3">
         <v>300</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,71 +4446,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5400</v>
       </c>
       <c r="H57" s="3">
         <v>5400</v>
       </c>
       <c r="I57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J57" s="3">
         <v>4200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,13 +4530,16 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -4414,11 +4548,11 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -4426,11 +4560,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4438,11 +4572,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4455,24 +4589,24 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>81600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4482,79 +4616,82 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E59" s="3">
         <v>10300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>30900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>36600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>36800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>28600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>31000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
@@ -4565,80 +4702,83 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E60" s="3">
         <v>65600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>60400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>60700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>54500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>41100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>41900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>33900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>116900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3">
         <v>200</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,71 +4788,74 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>463400</v>
+      </c>
+      <c r="E61" s="3">
         <v>460300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>429200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>393500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>394300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>377700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>331600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>330600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>337600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>349400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>338700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>332700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>318600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>292200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>278000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>277400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>269900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>225300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>203900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>244400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4731,34 +4874,37 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>500</v>
       </c>
       <c r="G62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H62" s="3">
         <v>600</v>
       </c>
       <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
-      </c>
-      <c r="K62" s="3">
-        <v>600</v>
       </c>
       <c r="L62" s="3">
         <v>600</v>
@@ -4767,35 +4913,35 @@
         <v>600</v>
       </c>
       <c r="N62" s="3">
+        <v>600</v>
+      </c>
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>36200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>26400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,80 +5218,83 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>571100</v>
+      </c>
+      <c r="E66" s="3">
         <v>567100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>531400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>486900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>498900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>471600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>419000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>413700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>429000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>436100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>430300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>415600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>404400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>376700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>343900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>341000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>337900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>291600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>263800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>387200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3">
         <v>200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5403,11 +5571,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>81600</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,79 +5680,82 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E72" s="3">
         <v>27000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3">
+        <v>0</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,79 +6024,82 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>377700</v>
+      </c>
+      <c r="E76" s="3">
         <v>373600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>370900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>368900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>364900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>359500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>357900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>353000</v>
       </c>
       <c r="K76" s="3">
         <v>353000</v>
       </c>
       <c r="L76" s="3">
-        <v>349800</v>
+        <v>353000</v>
       </c>
       <c r="M76" s="3">
         <v>349800</v>
       </c>
       <c r="N76" s="3">
+        <v>349800</v>
+      </c>
+      <c r="O76" s="3">
         <v>350500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>348400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>343600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>342700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>342300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>346400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>341400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>337900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>112200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>0</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,165 +6196,171 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E81" s="3">
         <v>2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2300</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
         <v>0</v>
       </c>
@@ -6175,11 +6370,14 @@
       <c r="AB81" s="3">
         <v>0</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6236,50 +6435,50 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>5400</v>
       </c>
       <c r="R83" s="3">
         <v>5400</v>
       </c>
       <c r="S83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="T83" s="3">
         <v>5200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3200</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,77 +6921,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>12900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10500</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
         <v>0</v>
       </c>
@@ -6787,11 +7004,14 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,19 +7041,20 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -6851,41 +7072,41 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-112200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,77 +7297,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-40400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-36700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-32000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-128100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-112700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21400</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7225,8 +7459,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,160 +7759,166 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>29700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>34000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>46900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>19200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>12700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>6500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>44000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>20800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>131800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>113600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>9000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>10000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3900</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
